--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="73">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3311,6 +3311,69 @@
     </rPh>
     <rPh sb="16" eb="18">
       <t>ソウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WSでの操作は完成した。しかしADの回転を変えていく必要あり。
+僕のやつが完成しないとマップの当たり判定が怪しいので、早急に完成させる必要あり
+暇な人が出ないように、チケットはなるべく多く様々な種類を用意しておく。</t>
+    <rPh sb="4" eb="6">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カイテン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ボク</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>アヤ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>サッキュウ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>ヒマ</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="76" eb="77">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="92" eb="93">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="94" eb="99">
+      <t>サマザマナシュルイ</t>
+    </rPh>
+    <rPh sb="100" eb="102">
+      <t>ヨウイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4354,7 +4417,9 @@
       <c r="B5" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="14"/>
+      <c r="C5" s="14" t="s">
+        <v>72</v>
+      </c>
       <c r="D5" s="15"/>
       <c r="E5" s="13"/>
     </row>

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3374,6 +3374,39 @@
     </rPh>
     <rPh sb="100" eb="102">
       <t>ヨウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・予想されるタスクのチケット化ができると作業分担がしやすくなるので、進められるといいですね。
+・作業予定の記載もお願いします。</t>
+    <rPh sb="1" eb="3">
+      <t>ヨソウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="20" eb="24">
+      <t>サギョウブンタン</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="48" eb="52">
+      <t>サギョウヨテイ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>ネガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4420,8 +4453,12 @@
       <c r="C5" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="13"/>
+      <c r="D5" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="108" customHeight="1">
       <c r="A6" s="12"/>

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3374,6 +3374,30 @@
     </rPh>
     <rPh sb="100" eb="102">
       <t>ヨウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・缶の操作をできるようにする</t>
+    <rPh sb="1" eb="2">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ソウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプや移動など基本的なものはできるようになった
+シャカシャカゲージのシステムを制作できた</t>
+    <rPh sb="5" eb="7">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>キホンテキ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>セイサク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4424,9 +4448,15 @@
       <c r="E5" s="13"/>
     </row>
     <row r="6" spans="1:5" ht="108" customHeight="1">
-      <c r="A6" s="12"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
+      <c r="A6" s="12">
+        <v>46121</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>74</v>
+      </c>
       <c r="D6" s="15"/>
       <c r="E6" s="13"/>
     </row>

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="77">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3398,6 +3398,39 @@
     </rPh>
     <rPh sb="41" eb="43">
       <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・翌営業日の予定の記載をお願いします。
+・一つ一つ仕上げていきましょう</t>
+    <rPh sb="1" eb="5">
+      <t>ヨクエイギョウビ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ネガ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>シア</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4457,8 +4490,12 @@
       <c r="C6" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="13"/>
+      <c r="D6" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="108" customHeight="1">
       <c r="A7" s="12"/>

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="77">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3398,6 +3398,43 @@
     </rPh>
     <rPh sb="41" eb="43">
       <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>缶を発射できるようにする。
+カメラを上に向けるようにする</t>
+    <rPh sb="0" eb="1">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハッシャ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラを上にはできるようになったが、発射はできない。
+コーラを噴出するのを早く作らなくては。</t>
+    <rPh sb="4" eb="5">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ハッシャ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>フンシュツ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ハヤ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4461,9 +4498,15 @@
       <c r="E6" s="13"/>
     </row>
     <row r="7" spans="1:5" ht="108" customHeight="1">
-      <c r="A7" s="12"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
+      <c r="A7" s="12">
+        <v>46122</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>76</v>
+      </c>
       <c r="D7" s="15"/>
       <c r="E7" s="13"/>
     </row>

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3435,6 +3435,33 @@
     </rPh>
     <rPh sb="39" eb="40">
       <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・そろそろGit上でコードをあげてもらえるといいかと。
+・翌日の作業予定の記載をお願いします。</t>
+    <rPh sb="8" eb="9">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ヨクジツ</t>
+    </rPh>
+    <rPh sb="32" eb="36">
+      <t>サギョウヨテイ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ネガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4507,8 +4534,12 @@
       <c r="C7" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="13"/>
+      <c r="D7" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="108" customHeight="1">
       <c r="A8" s="12"/>

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="78">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3434,6 +3434,23 @@
       <t>ハヤ</t>
     </rPh>
     <rPh sb="39" eb="40">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>缶を発射できるようにする。
+車のアルゴリズムを作る。</t>
+    <rPh sb="0" eb="1">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハッシャ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
       <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -4511,8 +4528,12 @@
       <c r="E7" s="13"/>
     </row>
     <row r="8" spans="1:5" ht="108" customHeight="1">
-      <c r="A8" s="12"/>
-      <c r="B8" s="14"/>
+      <c r="A8" s="12">
+        <v>46125</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>77</v>
+      </c>
       <c r="C8" s="14"/>
       <c r="D8" s="15"/>
       <c r="E8" s="13"/>

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="80">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3451,6 +3451,81 @@
       <t>クルマ</t>
     </rPh>
     <rPh sb="23" eb="24">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>缶の発射の仕組みは完成したが操作性にストレスを感じるため、
+新しく発射されている最中に、spaceキーを押すと落下する仕組みを作る。
+車のアルゴリズムを手を付けられていない。</t>
+    <rPh sb="0" eb="1">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハッシャ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ソウサセイ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ハッシャ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>サイチュウ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ラッカ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="76" eb="77">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・缶を落下させるプログラムをつくる。
+・車のアルゴリズムをプログラムする。
+・コインを獲得するプログラムを作る。</t>
+    <rPh sb="1" eb="2">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ラッカ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="53" eb="54">
       <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -4534,13 +4609,19 @@
       <c r="B8" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="14"/>
+      <c r="C8" s="14" t="s">
+        <v>78</v>
+      </c>
       <c r="D8" s="15"/>
       <c r="E8" s="13"/>
     </row>
     <row r="9" spans="1:5" ht="108" customHeight="1">
-      <c r="A9" s="12"/>
-      <c r="B9" s="14"/>
+      <c r="A9" s="12">
+        <v>46126</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="C9" s="14"/>
       <c r="D9" s="15"/>
       <c r="E9" s="13"/>

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="82">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3528,6 +3528,19 @@
     <rPh sb="53" eb="54">
       <t>ツク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・私のコメントが消えているのは作業報告の更新仕方に問題がありそうなので、確認してもらえると助かります。
+　作業報告を書く前に、pullで最新版を取得してから、記入・commit / push するようにしてみて下さい
+</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4612,8 +4625,12 @@
       <c r="C8" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="13"/>
+      <c r="D8" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="9" spans="1:5" ht="108" customHeight="1">
       <c r="A9" s="12">

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="84">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3541,6 +3541,76 @@
     <t xml:space="preserve">・私のコメントが消えているのは作業報告の更新仕方に問題がありそうなので、確認してもらえると助かります。
 　作業報告を書く前に、pullで最新版を取得してから、記入・commit / push するようにしてみて下さい
 </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>缶の動きはひとまず完成した。
+いまだに自分の思ってもいない方向へ発射されることもあるので
+それをあとで修正。
+現在車のアルゴリズムの作成中。道は長し。
+おかげさまですこしずつGitHubを使い方がわかった。</t>
+    <rPh sb="0" eb="1">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ハッシャ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="66" eb="69">
+      <t>サクセイチュウ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>ミチ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="94" eb="95">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="96" eb="97">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・車のアルゴリズムを制作。
+・ゴールをした時のUIを表示する。</t>
+    <rPh sb="1" eb="2">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ヒョウジ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4639,13 +4709,19 @@
       <c r="B9" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="14"/>
+      <c r="C9" s="14" t="s">
+        <v>82</v>
+      </c>
       <c r="D9" s="15"/>
       <c r="E9" s="13"/>
     </row>
     <row r="10" spans="1:5" ht="108" customHeight="1">
-      <c r="A10" s="12"/>
-      <c r="B10" s="14"/>
+      <c r="A10" s="12">
+        <v>46127</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>83</v>
+      </c>
       <c r="C10" s="14"/>
       <c r="D10" s="15"/>
       <c r="E10" s="13"/>

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="86">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3610,6 +3610,42 @@
     </rPh>
     <rPh sb="26" eb="28">
       <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・git はかなり難しいコード管理システムなので、まずはコードの共有と差分の確認ができればOKです。
+・一つずつ完成に近づけていきましょう！</t>
+    <rPh sb="9" eb="10">
+      <t>ムズカ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>キョウユウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>サブン</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>チカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4712,8 +4748,12 @@
       <c r="C9" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="13"/>
+      <c r="D9" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="108" customHeight="1">
       <c r="A10" s="12">

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="88">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3646,6 +3646,65 @@
     </rPh>
     <rPh sb="59" eb="60">
       <t>チカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>優先順位を考えて、車のアルゴリズムはやめて、ゲームクリアの処理を制作
+１７日までにゲームループの完成を目指す。
+・GitHubでマジがしなかった件もあり共同作業がしずらい雰囲気</t>
+    <rPh sb="0" eb="4">
+      <t>ユウセンジュンイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>メザ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="76" eb="80">
+      <t>キョウドウサギョウ</t>
+    </rPh>
+    <rPh sb="85" eb="88">
+      <t>フンイキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲームのクリア処理
+・NPCの地下づくと吹き飛ばされる処理。</t>
+    <rPh sb="8" eb="10">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ショリ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4762,13 +4821,19 @@
       <c r="B10" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="14"/>
+      <c r="C10" s="14" t="s">
+        <v>86</v>
+      </c>
       <c r="D10" s="15"/>
       <c r="E10" s="13"/>
     </row>
     <row r="11" spans="1:5" ht="108" customHeight="1">
-      <c r="A11" s="12"/>
-      <c r="B11" s="14"/>
+      <c r="A11" s="12">
+        <v>46128</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="C11" s="14"/>
       <c r="D11" s="15"/>
       <c r="E11" s="13"/>

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -3650,61 +3650,61 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>優先順位を考えて、車のアルゴリズムはやめて、ゲームクリアの処理を制作
-１７日までにゲームループの完成を目指す。
-・GitHubでマジがしなかった件もあり共同作業がしずらい雰囲気</t>
-    <rPh sb="0" eb="4">
-      <t>ユウセンジュンイ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>カンガ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>クルマ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>セイサク</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>ニチ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>メザ</t>
-    </rPh>
-    <rPh sb="72" eb="73">
-      <t>ケン</t>
-    </rPh>
-    <rPh sb="76" eb="80">
-      <t>キョウドウサギョウ</t>
-    </rPh>
-    <rPh sb="85" eb="88">
-      <t>フンイキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・ゲームのクリア処理
-・NPCの地下づくと吹き飛ばされる処理。</t>
+・NPCに近づくと吹き飛ばされる処理。</t>
     <rPh sb="8" eb="10">
       <t>ショリ</t>
     </rPh>
-    <rPh sb="16" eb="18">
+    <rPh sb="16" eb="17">
       <t>チカ</t>
     </rPh>
-    <rPh sb="21" eb="22">
+    <rPh sb="20" eb="21">
       <t>フ</t>
     </rPh>
-    <rPh sb="23" eb="24">
+    <rPh sb="22" eb="23">
       <t>ト</t>
     </rPh>
-    <rPh sb="28" eb="30">
+    <rPh sb="27" eb="29">
       <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・優先順位を考えて、車のアルゴリズムはやめて、ゲームクリアの処理を制作。
+・１７日までにゲームループの完成を目指す。
+・GitHubでマージがしなかった件もあり共同作業がしずらい雰囲気</t>
+    <rPh sb="1" eb="5">
+      <t>ユウセンジュンイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>メザ</t>
+    </rPh>
+    <rPh sb="76" eb="77">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="80" eb="84">
+      <t>キョウドウサギョウ</t>
+    </rPh>
+    <rPh sb="89" eb="92">
+      <t>フンイキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4822,7 +4822,7 @@
         <v>83</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="13"/>
@@ -4832,7 +4832,7 @@
         <v>46128</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="15"/>

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="90">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3705,6 +3705,45 @@
     </rPh>
     <rPh sb="89" eb="92">
       <t>フンイキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・優先順位は適宜見直していきましょう
+・まだ、GitHubのリポジトリ環境が整備できていない点で躓いているところも多そうです。こちらでも確認していきます。</t>
+    <rPh sb="1" eb="5">
+      <t>ユウセンジュンイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>テキギ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ミナオ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>セイビ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>ツマヅ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>カクニン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4824,8 +4863,12 @@
       <c r="C10" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="13"/>
+      <c r="D10" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="108" customHeight="1">
       <c r="A11" s="12">

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3744,6 +3744,55 @@
     </rPh>
     <rPh sb="68" eb="70">
       <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>githubのせいでほとんど時間が溶けた。
+次からはもっとうまく使おう
+NPCの処理はベータ版に移行
+ループの完成を目指す</t>
+    <rPh sb="14" eb="16">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>バン</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>メザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・アルファ版の完成…？
+・ゲームループを完成させる
+</t>
+    <rPh sb="5" eb="6">
+      <t>バン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カンセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4877,13 +4926,19 @@
       <c r="B11" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="14"/>
+      <c r="C11" s="14" t="s">
+        <v>90</v>
+      </c>
       <c r="D11" s="15"/>
       <c r="E11" s="13"/>
     </row>
     <row r="12" spans="1:5" ht="108" customHeight="1">
-      <c r="A12" s="12"/>
-      <c r="B12" s="14"/>
+      <c r="A12" s="12">
+        <v>46129</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>91</v>
+      </c>
       <c r="C12" s="14"/>
       <c r="D12" s="15"/>
       <c r="E12" s="13"/>

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="94">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3793,6 +3793,38 @@
     </rPh>
     <rPh sb="20" eb="22">
       <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・git で時間が解けるのはよくあることなので、git にpush して落としなおして動作確認するまでの時間も工数に入れるようにしましょう。</t>
+    <rPh sb="6" eb="8">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="43" eb="47">
+      <t>ドウサカクニン</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>コウスウ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>イ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4929,8 +4961,12 @@
       <c r="C11" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="13"/>
+      <c r="D11" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="108" customHeight="1">
       <c r="A12" s="12">

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="96">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3825,6 +3825,43 @@
     </rPh>
     <rPh sb="58" eb="59">
       <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・アルファ版完成
+・ゲームループの流れが完成した。
+・仕事の割り振りが難しい。</t>
+    <rPh sb="5" eb="6">
+      <t>バン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シゴト</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ムズカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>車のアルゴリズム</t>
+    <rPh sb="0" eb="1">
+      <t>クルマ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4975,13 +5012,19 @@
       <c r="B12" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="C12" s="14"/>
+      <c r="C12" s="14" t="s">
+        <v>94</v>
+      </c>
       <c r="D12" s="15"/>
       <c r="E12" s="13"/>
     </row>
     <row r="13" spans="1:5" ht="108" customHeight="1">
-      <c r="A13" s="12"/>
-      <c r="B13" s="14"/>
+      <c r="A13" s="12">
+        <v>46132</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>95</v>
+      </c>
       <c r="C13" s="14"/>
       <c r="D13" s="15"/>
       <c r="E13" s="13"/>

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="98">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3862,6 +3862,57 @@
     <t>車のアルゴリズム</t>
     <rPh sb="0" eb="1">
       <t>クルマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・まずは仕事をチケットに分解するところから始めましょう
+　チケットを提示して、各自やりたいものを取っていく　というスタイルがアジャイル系の開発スタイルなので、割り振りよりタスクの大きさを気にすると良いです。</t>
+    <rPh sb="4" eb="6">
+      <t>シゴト</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ブンカイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>テイジ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>カクジ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="79" eb="80">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="81" eb="82">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="89" eb="90">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="93" eb="94">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="98" eb="99">
+      <t>イ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5015,8 +5066,12 @@
       <c r="C12" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="13"/>
+      <c r="D12" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="108" customHeight="1">
       <c r="A13" s="12">

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="100">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3913,6 +3913,97 @@
     </rPh>
     <rPh sb="98" eb="99">
       <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・優先順位を今一度考え、車のアルゴリズムは後回し。
+・タイマーの作成。
+→　GitHubでマージができずデータが消えたため未完成
+・缶のプログラムを自販機で能力を変えれるように設定。
+・ポーズ画面の制作中。
+・作ったオブジェクトが消えるため、絶望缶がすごい。</t>
+    <rPh sb="1" eb="5">
+      <t>ユウセンジュンイ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>イマイチド</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>アトマワ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="61" eb="64">
+      <t>ミカンセイ</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="74" eb="77">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="81" eb="82">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="96" eb="98">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="99" eb="102">
+      <t>セイサクチュウ</t>
+    </rPh>
+    <rPh sb="105" eb="106">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="115" eb="116">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="121" eb="123">
+      <t>ゼツボウ</t>
+    </rPh>
+    <rPh sb="123" eb="124">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ポーズ画面の制作
+・タイマーの作成
+・ごみ箱スコアの見直し
+・トータルスコアの計算</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ミナオ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ケイサン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5080,13 +5171,19 @@
       <c r="B13" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C13" s="14"/>
+      <c r="C13" s="14" t="s">
+        <v>98</v>
+      </c>
       <c r="D13" s="15"/>
       <c r="E13" s="13"/>
     </row>
     <row r="14" spans="1:5" ht="108" customHeight="1">
-      <c r="A14" s="12"/>
-      <c r="B14" s="14"/>
+      <c r="A14" s="12">
+        <v>46133</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>99</v>
+      </c>
       <c r="C14" s="14"/>
       <c r="D14" s="15"/>
       <c r="E14" s="13"/>

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="104">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4004,6 +4004,83 @@
     </rPh>
     <rPh sb="40" eb="42">
       <t>ケイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポーズ画面とタイマーの制作成功。
+一度githubでデータを消しかけたため
+今日はほとんどそちらに時間を割いてしまった。</t>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>セイサクセイコウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トータルスコアの計算
+・車のアルゴリズム</t>
+    <rPh sb="8" eb="10">
+      <t>ケイサン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>クルマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>面談にて時間なし
+現状の確認のみ実施完了</t>
+    <rPh sb="0" eb="2">
+      <t>メンダン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ゲンジョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポーズ画面やリザルト画面の細かな調整。</t>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>コマ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>チョウセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5184,20 +5261,32 @@
       <c r="B14" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="14"/>
+      <c r="C14" s="14" t="s">
+        <v>100</v>
+      </c>
       <c r="D14" s="15"/>
       <c r="E14" s="13"/>
     </row>
     <row r="15" spans="1:5" ht="108" customHeight="1">
-      <c r="A15" s="12"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
+      <c r="A15" s="12">
+        <v>46134</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>102</v>
+      </c>
       <c r="D15" s="15"/>
       <c r="E15" s="13"/>
     </row>
     <row r="16" spans="1:5" ht="108" customHeight="1">
-      <c r="A16" s="12"/>
-      <c r="B16" s="14"/>
+      <c r="A16" s="12">
+        <v>46135</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>103</v>
+      </c>
       <c r="C16" s="14"/>
       <c r="D16" s="15"/>
       <c r="E16" s="13"/>

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="106">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4081,6 +4081,20 @@
     </rPh>
     <rPh sb="16" eb="18">
       <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・承知しました</t>
+    <rPh sb="1" eb="3">
+      <t>ショウチ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5277,8 +5291,12 @@
       <c r="C15" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="13"/>
+      <c r="D15" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="108" customHeight="1">
       <c r="A16" s="12">

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="108">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4095,6 +4095,61 @@
     <t>・承知しました</t>
     <rPh sb="1" eb="3">
       <t>ショウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>調整完了
+データが全部消えたり、文字化けしたりしてかなりまずかったが、
+リカバリーがうまくいき何とかなった。
+クリア時にカメラが動くように変更</t>
+    <rPh sb="0" eb="4">
+      <t>チョウセイカンリョウ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ゼンブキ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>モジバ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ナン</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="64" eb="65">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームオーバー画面の表示。
+車の制作
+降下の切り替え</t>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>カ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5305,13 +5360,19 @@
       <c r="B16" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C16" s="14"/>
+      <c r="C16" s="14" t="s">
+        <v>106</v>
+      </c>
       <c r="D16" s="15"/>
       <c r="E16" s="13"/>
     </row>
     <row r="17" spans="1:5" ht="108" customHeight="1">
-      <c r="A17" s="12"/>
-      <c r="B17" s="14"/>
+      <c r="A17" s="12">
+        <v>46136</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>107</v>
+      </c>
       <c r="C17" s="14"/>
       <c r="D17" s="15"/>
       <c r="E17" s="13"/>

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="110">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4150,6 +4150,49 @@
     </rPh>
     <rPh sb="24" eb="25">
       <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベータ版製作終了
+ゲームループが完成したかが危うい
+自販機のマージが失敗。
+くるしい</t>
+    <rPh sb="3" eb="6">
+      <t>バンセイサク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>アヤ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>シッパイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BGM
+缶に音をつける
+自販機都のマージ再挑戦</t>
+    <rPh sb="4" eb="5">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>ジハンキト</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>サイチョウセン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5373,13 +5416,19 @@
       <c r="B17" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="C17" s="14"/>
+      <c r="C17" s="14" t="s">
+        <v>108</v>
+      </c>
       <c r="D17" s="15"/>
       <c r="E17" s="13"/>
     </row>
     <row r="18" spans="1:5" ht="108" customHeight="1">
-      <c r="A18" s="12"/>
-      <c r="B18" s="14"/>
+      <c r="A18" s="12">
+        <v>46137</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>109</v>
+      </c>
       <c r="C18" s="14"/>
       <c r="D18" s="15"/>
       <c r="E18" s="13"/>

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="112">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4193,6 +4193,33 @@
     </rPh>
     <rPh sb="20" eb="23">
       <t>サイチョウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・あまり思いつめないように
+・Gitでの共有がうまくいかない原因をハッキリさせた方がいいかもしれないですね。相談してください。</t>
+    <rPh sb="4" eb="5">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>キョウユウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ソウダン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5419,8 +5446,12 @@
       <c r="C17" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="13"/>
+      <c r="D17" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="18" spans="1:5" ht="108" customHeight="1">
       <c r="A18" s="12">

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="114">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4220,6 +4220,58 @@
     </rPh>
     <rPh sb="54" eb="56">
       <t>ソウダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームループの本完成。
+自販機のマージ成功。
+そのかわり、NPCがマージ失敗。消失
+→outlookでパッケージを送る。
+缶に音をつける作業途中。</t>
+    <rPh sb="7" eb="10">
+      <t>ホンカンセイ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ショウシツ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>缶に音をつける
+いよいよ車のアルゴリズム。</t>
+    <rPh sb="0" eb="1">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>クルマ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5455,18 +5507,24 @@
     </row>
     <row r="18" spans="1:5" ht="108" customHeight="1">
       <c r="A18" s="12">
-        <v>46137</v>
+        <v>46139</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="14"/>
+      <c r="C18" s="14" t="s">
+        <v>112</v>
+      </c>
       <c r="D18" s="15"/>
       <c r="E18" s="13"/>
     </row>
     <row r="19" spans="1:5" ht="108" customHeight="1">
-      <c r="A19" s="12"/>
-      <c r="B19" s="14"/>
+      <c r="A19" s="12">
+        <v>46140</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>113</v>
+      </c>
       <c r="C19" s="14"/>
       <c r="D19" s="15"/>
       <c r="E19" s="13"/>

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="116">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4272,6 +4272,53 @@
     </rPh>
     <rPh sb="12" eb="13">
       <t>クルマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>車のアルゴリズム制作完了。
+能力自販機を実装したが
+おそらく消える</t>
+    <rPh sb="0" eb="1">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>車の配置
+能力自販機の実装</t>
+    <rPh sb="0" eb="1">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジッソウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5525,13 +5572,19 @@
       <c r="B19" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="C19" s="14"/>
+      <c r="C19" s="14" t="s">
+        <v>114</v>
+      </c>
       <c r="D19" s="15"/>
       <c r="E19" s="13"/>
     </row>
     <row r="20" spans="1:5" ht="108" customHeight="1">
-      <c r="A20" s="12"/>
-      <c r="B20" s="14"/>
+      <c r="A20" s="12">
+        <v>46149</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>115</v>
+      </c>
       <c r="C20" s="14"/>
       <c r="D20" s="15"/>
       <c r="E20" s="13"/>

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="118">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4319,6 +4319,69 @@
     </rPh>
     <rPh sb="11" eb="13">
       <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>demo_city_night.unity に多人数で手を加える形になってしまっているところが難しいですね。
+シーンファイル(.unity)のマージは難しいので、修正手順を割り出してから、最新のdemo_city_night.unity に修正を加え、その間他の人がいじらないように制御する必要があるはずです。</t>
+    <rPh sb="23" eb="26">
+      <t>タニンズウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>カタチ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ムズカ</t>
+    </rPh>
+    <rPh sb="75" eb="76">
+      <t>ムズカ</t>
+    </rPh>
+    <rPh sb="81" eb="85">
+      <t>シュウセイテジュン</t>
+    </rPh>
+    <rPh sb="86" eb="87">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="88" eb="89">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>サイシン</t>
+    </rPh>
+    <rPh sb="120" eb="122">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="123" eb="124">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="128" eb="129">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="129" eb="130">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="131" eb="132">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="141" eb="143">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="145" eb="147">
+      <t>ヒツヨウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5575,8 +5638,12 @@
       <c r="C19" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="13"/>
+      <c r="D19" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="20" spans="1:5" ht="108" customHeight="1">
       <c r="A20" s="12">

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="118">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4319,6 +4319,41 @@
     </rPh>
     <rPh sb="11" eb="13">
       <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>車の設置完了！
+缶の効果音付け完了！
+まにあわなかったよー</t>
+    <rPh sb="0" eb="1">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>セッチカンリョウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まにあわせるよー
+違和感の修正</t>
+    <rPh sb="9" eb="12">
+      <t>イワカン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シュウセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5585,13 +5620,19 @@
       <c r="B20" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="C20" s="14"/>
+      <c r="C20" s="14" t="s">
+        <v>116</v>
+      </c>
       <c r="D20" s="15"/>
       <c r="E20" s="13"/>
     </row>
     <row r="21" spans="1:5" ht="108" customHeight="1">
-      <c r="A21" s="12"/>
-      <c r="B21" s="14"/>
+      <c r="A21" s="12">
+        <v>46150</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>117</v>
+      </c>
       <c r="C21" s="14"/>
       <c r="D21" s="15"/>
       <c r="E21" s="13"/>

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="120">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4382,6 +4382,29 @@
     </rPh>
     <rPh sb="145" eb="147">
       <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・進捗と作業予定の記載をお願いします。</t>
+    <rPh sb="1" eb="3">
+      <t>シンチョク</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>サギョウヨテイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ネガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5653,8 +5676,12 @@
         <v>115</v>
       </c>
       <c r="C20" s="14"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="13"/>
+      <c r="D20" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="21" spans="1:5" ht="108" customHeight="1">
       <c r="A21" s="12"/>

--- a/Reports/04_takumu_kobayashi_作業報告.xlsx
+++ b/Reports/04_takumu_kobayashi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="123">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4405,6 +4405,44 @@
     </rPh>
     <rPh sb="13" eb="14">
       <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>書いたのに消えた</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完成させる。
+車の実装</t>
+    <rPh sb="0" eb="2">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まだ未完成だけど発表できるレベルにはなった。
+これからは人力でマージをしていく。</t>
+    <rPh sb="2" eb="5">
+      <t>ミカンセイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハッピョウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ジンリキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5675,7 +5713,9 @@
       <c r="B20" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="C20" s="14"/>
+      <c r="C20" s="14" t="s">
+        <v>120</v>
+      </c>
       <c r="D20" s="15" t="s">
         <v>118</v>
       </c>
@@ -5684,9 +5724,15 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="108" customHeight="1">
-      <c r="A21" s="12"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
+      <c r="A21" s="12">
+        <v>46150</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>122</v>
+      </c>
       <c r="D21" s="15"/>
       <c r="E21" s="13"/>
     </row>
